--- a/docs/xls/dataset_list.xlsx
+++ b/docs/xls/dataset_list.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\ha\dev\bgslibrary-examples-python\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\NextCloud\paper2_main\docs\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BA04513-ABE8-4DE1-8E36-68E4A54B839E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8E24E38-E1DA-45B8-BACA-954EB846FCF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="285" windowWidth="16440" windowHeight="28035" xr2:uid="{AD7D0BE0-3F31-48AD-9A26-171496877D99}"/>
+    <workbookView xWindow="17010" yWindow="-120" windowWidth="28110" windowHeight="16440" xr2:uid="{AD7D0BE0-3F31-48AD-9A26-171496877D99}"/>
   </bookViews>
   <sheets>
     <sheet name="all_dataset_list" sheetId="1" r:id="rId1"/>
